--- a/financial_models/opportunities/3998.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3998.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2CAD844F-ACA2-4A02-8F89-C2DB4D4D8D3B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82555181-86BB-4624-874D-6A9B9715B427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,25 +5022,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.17</v>
+        <v>4.3</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>48724.247706239999</v>
+        <v>50243.229049599999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.15311413376648342</v>
+        <v>0.14074374255347319</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5558,13 +5558,13 @@
       </c>
       <c r="C22" s="255">
         <f>E140</f>
-        <v>3.0048792225964673</v>
+        <v>2.970225604821576</v>
       </c>
       <c r="D22" s="38" t="s">
         <v>405</v>
       </c>
       <c r="E22" s="79">
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -5573,13 +5573,13 @@
       </c>
       <c r="C23" s="256">
         <f>E141</f>
-        <v>3.7171121620548737</v>
+        <v>3.7237185496487291</v>
       </c>
       <c r="D23" s="38" t="s">
         <v>406</v>
       </c>
       <c r="E23" s="443">
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.9966797023031449E-2</v>
+        <v>6.7851521764195608E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.235011990407674E-2</v>
+        <v>6.0465116279069774E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6582,19 +6582,19 @@
       </c>
       <c r="C140" s="333">
         <f>Scenarios!C62</f>
-        <v>0.47576140978863113</v>
+        <v>0.47218934911242616</v>
       </c>
       <c r="D140" s="333">
         <f>Scenarios!D62</f>
-        <v>2.5291178128078364</v>
+        <v>2.4980362557091498</v>
       </c>
       <c r="E140" s="334">
         <f>Scenarios!E62</f>
-        <v>3.0048792225964673</v>
+        <v>2.970225604821576</v>
       </c>
       <c r="F140" s="335">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -6603,19 +6603,19 @@
       </c>
       <c r="C141" s="333">
         <f>Scenarios!C63</f>
-        <v>0.54704102628996054</v>
+        <v>0.54768518518518516</v>
       </c>
       <c r="D141" s="333">
         <f>Scenarios!D63</f>
-        <v>3.1700711357649132</v>
+        <v>3.1760333644635437</v>
       </c>
       <c r="E141" s="334">
         <f>Scenarios!E63</f>
-        <v>3.7171121620548737</v>
+        <v>3.7237185496487291</v>
       </c>
       <c r="F141" s="335">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="142" spans="1:6">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,18 +6793,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6821,6 +6809,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14075,16 +14075,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.235011990407674E-2</v>
+        <v>6.0465116279069774E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.235011990407674E-2</v>
+        <v>6.0465116279069774E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.9952038369304558E-2</v>
+        <v>5.8139534883720929E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15296,34 +15296,34 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.9966797023031449E-2</v>
+        <v>6.7851521764195608E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.233048942706626E-2</v>
+        <v>6.0446079281596815E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.6426662299376755E-2</v>
+        <v>5.472073995079095E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.18814885049510124</v>
+        <v>0.18246062943362143</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.18669646778889504</v>
+        <v>0.18105215597202148</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.15020513678130981</v>
+        <v>0.14566405125071208</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.12814132319482283</v>
+        <v>0.12426728319125843</v>
       </c>
       <c r="M124" s="74" t="str">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
@@ -15353,27 +15353,27 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.2915297151832856E-2</v>
+        <v>7.0710881191428612E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.4036617226219616E-2</v>
+        <v>6.2100626472868792E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.3891370327429763E-2</v>
+        <v>4.2564421922181885E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2326420562382193E-2</v>
+        <v>4.1046784591891566E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.5086555062009916E-2</v>
+        <v>3.402579874618171E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4693741958911993E-2</v>
+        <v>2.3947186969456514E-2</v>
       </c>
       <c r="M125" s="22" t="str">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19815,7 +19815,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.17</v>
+        <v>4.3</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19826,7 +19826,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.15311413376648342</v>
+        <v>0.14074374255347319</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20099,23 +20099,23 @@
       </c>
       <c r="C62" s="119">
         <f>PV(F62, Holding_Period, -C58, 0)</f>
-        <v>0.47576140978863113</v>
+        <v>0.47218934911242616</v>
       </c>
       <c r="D62" s="119">
         <f>C36/(1+F62)^Holding_Period</f>
-        <v>2.5291178128078364</v>
+        <v>2.4980362557091498</v>
       </c>
       <c r="E62" s="332">
         <f>C62+D62</f>
-        <v>3.0048792225964673</v>
+        <v>2.970225604821576</v>
       </c>
       <c r="F62" s="301">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
       <c r="G62" s="440">
         <f>(1-E62/C36)</f>
-        <v>0.45248222050948106</v>
+        <v>0.45879644163116295</v>
       </c>
     </row>
     <row r="63" spans="2:7" ht="13.15">
@@ -20124,23 +20124,23 @@
       </c>
       <c r="C63" s="119">
         <f>PV(F63, Holding_Period, -C58, 0)</f>
-        <v>0.54704102628996054</v>
+        <v>0.54768518518518516</v>
       </c>
       <c r="D63" s="119">
         <f>C36/(1+F63)^Holding_Period</f>
-        <v>3.1700711357649132</v>
+        <v>3.1760333644635437</v>
       </c>
       <c r="E63" s="332">
         <f>C63+D63</f>
-        <v>3.7171121620548737</v>
+        <v>3.7237185496487291</v>
       </c>
       <c r="F63" s="301">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
       <c r="G63" s="440">
         <f>(1-E63/C36)</f>
-        <v>0.32270655613009425</v>
+        <v>0.32150280902483919</v>
       </c>
     </row>
     <row r="65" spans="2:7" ht="13.15">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.17</v>
+        <v>4.3</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20340,14 +20340,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>48724.247706239999</v>
+        <v>50243.229049599999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.15311413376648342</v>
+        <v>0.14074374255347319</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20355,13 +20355,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20477,14 +20477,14 @@
       </c>
       <c r="C22" s="364">
         <f>E140</f>
-        <v>3.0048792225964673</v>
+        <v>2.970225604821576</v>
       </c>
       <c r="D22" s="365" t="s">
         <v>439</v>
       </c>
       <c r="E22" s="366">
         <f>Thesis!E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="23" spans="1:6">
@@ -20493,14 +20493,14 @@
       </c>
       <c r="C23" s="367">
         <f>E141</f>
-        <v>3.7171121620548737</v>
+        <v>3.7237185496487291</v>
       </c>
       <c r="D23" s="365" t="s">
         <v>440</v>
       </c>
       <c r="E23" s="368">
         <f>Thesis!E23</f>
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="24" spans="1:6">
@@ -20546,22 +20546,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20751,10 +20751,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20770,22 +20770,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20819,7 +20819,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.9966797023031449E-2</v>
+        <v>6.7851521764195608E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>6.235011990407674E-2</v>
+        <v>6.0465116279069774E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20920,22 +20920,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20943,13 +20943,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21098,33 +21098,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21187,23 +21187,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21247,13 +21247,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21417,13 +21417,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21436,22 +21436,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21512,19 +21512,19 @@
       </c>
       <c r="C140" s="409">
         <f>Scenarios!C62</f>
-        <v>0.47576140978863113</v>
+        <v>0.47218934911242616</v>
       </c>
       <c r="D140" s="409">
         <f>Scenarios!D62</f>
-        <v>2.5291178128078364</v>
+        <v>2.4980362557091498</v>
       </c>
       <c r="E140" s="410">
         <f>Scenarios!E62</f>
-        <v>3.0048792225964673</v>
+        <v>2.970225604821576</v>
       </c>
       <c r="F140" s="411">
         <f>E22</f>
-        <v>0.29465259038036601</v>
+        <v>0.3</v>
       </c>
     </row>
     <row r="141" spans="1:6">
@@ -21533,19 +21533,19 @@
       </c>
       <c r="C141" s="409">
         <f>Scenarios!C63</f>
-        <v>0.54704102628996054</v>
+        <v>0.54768518518518516</v>
       </c>
       <c r="D141" s="409">
         <f>Scenarios!D63</f>
-        <v>3.1700711357649132</v>
+        <v>3.1760333644635437</v>
       </c>
       <c r="E141" s="410">
         <f>Scenarios!E63</f>
-        <v>3.7171121620548737</v>
+        <v>3.7237185496487291</v>
       </c>
       <c r="F141" s="411">
         <f>Scenarios!F63</f>
-        <v>0.20075184365903001</v>
+        <v>0.2</v>
       </c>
     </row>
     <row r="143" spans="1:6">
@@ -21620,13 +21620,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21634,13 +21634,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21677,22 +21677,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21716,15 +21716,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21739,12 +21736,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3998.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3998.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{82555181-86BB-4624-874D-6A9B9715B427}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EBD2FF7-D4F7-4F5A-A713-8DCEF3B62546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,6 +5022,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5031,16 +5040,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.3</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>50243.229049599999</v>
+        <v>49892.694893439992</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.14074374255347319</v>
+        <v>0.14355222054606112</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.7851521764195608E-2</v>
+        <v>6.8328230348019006E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.0465116279069774E-2</v>
+        <v>6.0889929742388764E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,6 +6793,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6809,18 +6821,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14075,16 +14075,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.0465116279069774E-2</v>
+        <v>6.0889929742388764E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.0465116279069774E-2</v>
+        <v>6.0889929742388764E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8139534883720929E-2</v>
+        <v>5.8548009367681501E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15296,34 +15296,34 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.7851521764195608E-2</v>
+        <v>6.8328230348019006E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.0446079281596815E-2</v>
+        <v>6.0870758995519046E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.472073995079095E-2</v>
+        <v>5.5105194798220396E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.18246062943362143</v>
+        <v>0.18374255423057897</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.18105215597202148</v>
+        <v>0.18232418517088814</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.14566405125071208</v>
+        <v>0.14668745207917142</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.12426728319125843</v>
+        <v>0.12514035543850383</v>
       </c>
       <c r="M124" s="74" t="str">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
@@ -15353,27 +15353,27 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.0710881191428612E-2</v>
+        <v>7.1207678951555747E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2100626472868792E-2</v>
+        <v>6.2536930640125485E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2564421922181885E-2</v>
+        <v>4.2863469382993472E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.1046784591891566E-2</v>
+        <v>4.1335169495347483E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.402579874618171E-2</v>
+        <v>3.4264855880229823E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.3947186969456514E-2</v>
+        <v>2.4115434184698598E-2</v>
       </c>
       <c r="M125" s="22" t="str">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19815,7 +19815,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.3</v>
+        <v>4.2699999999999996</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19826,7 +19826,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.14074374255347319</v>
+        <v>0.14355222054606112</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.3</v>
+        <v>4.2699999999999996</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20340,14 +20340,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>50243.229049599999</v>
+        <v>49892.694893439992</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.14074374255347319</v>
+        <v>0.14355222054606112</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20355,13 +20355,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20546,22 +20546,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20751,10 +20751,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20770,22 +20770,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20819,7 +20819,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.7851521764195608E-2</v>
+        <v>6.8328230348019006E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>6.0465116279069774E-2</v>
+        <v>6.0889929742388764E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20920,22 +20920,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20943,13 +20943,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21098,33 +21098,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21187,23 +21187,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21247,13 +21247,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21417,13 +21417,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21436,22 +21436,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21620,13 +21620,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21634,13 +21634,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21677,22 +21677,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21716,12 +21716,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21736,15 +21739,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3998.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3998.HK_Valuation.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29822"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29929"/>
   <workbookPr showObjects="none" codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2EBD2FF7-D4F7-4F5A-A713-8DCEF3B62546}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD33817-BFA2-4B7B-9FEA-2735C409A79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,25 +5022,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.2699999999999996</v>
+        <v>4.32</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>49892.694893439992</v>
+        <v>50476.918487039999</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.14355222054606112</v>
+        <v>0.13888640390130119</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.8328230348019006E-2</v>
+        <v>6.7537394348620633E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.0889929742388764E-2</v>
+        <v>6.0185185185185182E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,18 +6793,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6821,6 +6809,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14075,16 +14075,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.0889929742388764E-2</v>
+        <v>6.0185185185185182E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.0889929742388764E-2</v>
+        <v>6.0185185185185182E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.8548009367681501E-2</v>
+        <v>5.7870370370370364E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15296,34 +15296,34 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.8328230348019006E-2</v>
+        <v>6.7537394348620633E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.0870758995519046E-2</v>
+        <v>6.0166236321959783E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.5105194798220396E-2</v>
+        <v>5.4467403191759502E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.18374255423057897</v>
+        <v>0.18161590429735464</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.18232418517088814</v>
+        <v>0.18021395154622505</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.14668745207917142</v>
+        <v>0.14498968064306988</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.12514035543850383</v>
+        <v>0.12369197169500259</v>
       </c>
       <c r="M124" s="74" t="str">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
@@ -15353,27 +15353,27 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.1207678951555747E-2</v>
+        <v>7.038351600072755E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.2536930640125485E-2</v>
+        <v>6.1813123572531437E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2863469382993472E-2</v>
+        <v>4.2367364413282892E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.1335169495347483E-2</v>
+        <v>4.0856753181743921E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.4264855880229823E-2</v>
+        <v>3.3868271900134569E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.4115434184698598E-2</v>
+        <v>2.3836320363116434E-2</v>
       </c>
       <c r="M125" s="22" t="str">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19815,7 +19815,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.2699999999999996</v>
+        <v>4.32</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19826,7 +19826,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.14355222054606112</v>
+        <v>0.13888640390130119</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.2699999999999996</v>
+        <v>4.32</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20340,14 +20340,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>49892.694893439992</v>
+        <v>50476.918487039999</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.14355222054606112</v>
+        <v>0.13888640390130119</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20355,13 +20355,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20546,22 +20546,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20751,10 +20751,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20770,22 +20770,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20819,7 +20819,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.8328230348019006E-2</v>
+        <v>6.7537394348620633E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>6.0889929742388764E-2</v>
+        <v>6.0185185185185182E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20920,22 +20920,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20943,13 +20943,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21098,33 +21098,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21187,23 +21187,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21247,13 +21247,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21417,13 +21417,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21436,22 +21436,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21620,13 +21620,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21634,13 +21634,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21677,22 +21677,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21716,15 +21716,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21739,12 +21736,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3998.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3998.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5DD33817-BFA2-4B7B-9FEA-2735C409A79A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E30E3FF-0CF7-4CB1-9DA6-B40A3843E6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,6 +5022,15 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
@@ -5031,16 +5040,7 @@
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="462" t="s">
+      <c r="B12" s="460" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="462"/>
-      <c r="D12" s="462"/>
-      <c r="E12" s="462"/>
-      <c r="F12" s="462"/>
+      <c r="C12" s="460"/>
+      <c r="D12" s="460"/>
+      <c r="E12" s="460"/>
+      <c r="F12" s="460"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="462" t="s">
+      <c r="B29" s="460" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="462"/>
-      <c r="D29" s="462"/>
-      <c r="E29" s="462"/>
-      <c r="F29" s="462"/>
+      <c r="C29" s="460"/>
+      <c r="D29" s="460"/>
+      <c r="E29" s="460"/>
+      <c r="F29" s="460"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="466" t="s">
+      <c r="B30" s="462" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="466"/>
-      <c r="D30" s="466"/>
-      <c r="E30" s="466"/>
-      <c r="F30" s="466"/>
+      <c r="C30" s="462"/>
+      <c r="D30" s="462"/>
+      <c r="E30" s="462"/>
+      <c r="F30" s="462"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="463" t="s">
+      <c r="B33" s="461" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="463"/>
-      <c r="D33" s="463"/>
-      <c r="E33" s="463"/>
-      <c r="F33" s="463"/>
+      <c r="C33" s="461"/>
+      <c r="D33" s="461"/>
+      <c r="E33" s="461"/>
+      <c r="F33" s="461"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="463" t="s">
+      <c r="B36" s="461" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="463"/>
-      <c r="D36" s="463"/>
-      <c r="E36" s="463"/>
-      <c r="F36" s="463"/>
+      <c r="C36" s="461"/>
+      <c r="D36" s="461"/>
+      <c r="E36" s="461"/>
+      <c r="F36" s="461"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="463" t="s">
+      <c r="B40" s="461" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="463"/>
-      <c r="D40" s="463"/>
-      <c r="E40" s="463"/>
-      <c r="F40" s="463"/>
+      <c r="C40" s="461"/>
+      <c r="D40" s="461"/>
+      <c r="E40" s="461"/>
+      <c r="F40" s="461"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="463" t="s">
+      <c r="B43" s="461" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="463"/>
-      <c r="D43" s="463"/>
-      <c r="E43" s="463"/>
-      <c r="F43" s="463"/>
+      <c r="C43" s="461"/>
+      <c r="D43" s="461"/>
+      <c r="E43" s="461"/>
+      <c r="F43" s="461"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="463" t="s">
+      <c r="B51" s="461" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="463"/>
-      <c r="D51" s="463"/>
-      <c r="E51" s="463"/>
-      <c r="F51" s="463"/>
+      <c r="C51" s="461"/>
+      <c r="D51" s="461"/>
+      <c r="E51" s="461"/>
+      <c r="F51" s="461"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="463" t="s">
+      <c r="B54" s="461" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="462" t="s">
+      <c r="B57" s="460" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="462"/>
-      <c r="D57" s="462"/>
-      <c r="E57" s="462"/>
-      <c r="F57" s="462"/>
+      <c r="C57" s="460"/>
+      <c r="D57" s="460"/>
+      <c r="E57" s="460"/>
+      <c r="F57" s="460"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="462" t="s">
+      <c r="B58" s="460" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="462"/>
-      <c r="D58" s="462"/>
-      <c r="E58" s="462"/>
-      <c r="F58" s="462"/>
+      <c r="C58" s="460"/>
+      <c r="D58" s="460"/>
+      <c r="E58" s="460"/>
+      <c r="F58" s="460"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="462" t="s">
+      <c r="B73" s="460" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="462"/>
-      <c r="D73" s="462"/>
-      <c r="E73" s="462"/>
-      <c r="F73" s="462"/>
+      <c r="C73" s="460"/>
+      <c r="D73" s="460"/>
+      <c r="E73" s="460"/>
+      <c r="F73" s="460"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="462" t="s">
+      <c r="B77" s="460" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="462"/>
-      <c r="D77" s="462"/>
-      <c r="E77" s="462"/>
-      <c r="F77" s="462"/>
+      <c r="C77" s="460"/>
+      <c r="D77" s="460"/>
+      <c r="E77" s="460"/>
+      <c r="F77" s="460"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="462" t="s">
+      <c r="B96" s="460" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="462"/>
-      <c r="D96" s="462"/>
-      <c r="E96" s="462"/>
-      <c r="F96" s="462"/>
+      <c r="C96" s="460"/>
+      <c r="D96" s="460"/>
+      <c r="E96" s="460"/>
+      <c r="F96" s="460"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="466" t="s">
+      <c r="B97" s="462" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="466"/>
-      <c r="D97" s="466"/>
-      <c r="E97" s="466"/>
-      <c r="F97" s="466"/>
+      <c r="C97" s="462"/>
+      <c r="D97" s="462"/>
+      <c r="E97" s="462"/>
+      <c r="F97" s="462"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="466" t="s">
+      <c r="B98" s="462" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="466"/>
-      <c r="D98" s="466"/>
-      <c r="E98" s="466"/>
-      <c r="F98" s="466"/>
+      <c r="C98" s="462"/>
+      <c r="D98" s="462"/>
+      <c r="E98" s="462"/>
+      <c r="F98" s="462"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="462" t="s">
+      <c r="B107" s="460" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="462"/>
-      <c r="D107" s="462"/>
-      <c r="E107" s="462"/>
-      <c r="F107" s="462"/>
+      <c r="C107" s="460"/>
+      <c r="D107" s="460"/>
+      <c r="E107" s="460"/>
+      <c r="F107" s="460"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="462" t="s">
+      <c r="B108" s="460" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="462"/>
-      <c r="D108" s="462"/>
-      <c r="E108" s="462"/>
-      <c r="F108" s="462"/>
+      <c r="C108" s="460"/>
+      <c r="D108" s="460"/>
+      <c r="E108" s="460"/>
+      <c r="F108" s="460"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="462" t="s">
+      <c r="B114" s="460" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="462"/>
-      <c r="D114" s="462"/>
-      <c r="E114" s="462"/>
-      <c r="F114" s="462"/>
+      <c r="C114" s="460"/>
+      <c r="D114" s="460"/>
+      <c r="E114" s="460"/>
+      <c r="F114" s="460"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="463" t="s">
+      <c r="B124" s="461" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="463"/>
-      <c r="D124" s="463"/>
-      <c r="E124" s="463"/>
-      <c r="F124" s="463"/>
+      <c r="C124" s="461"/>
+      <c r="D124" s="461"/>
+      <c r="E124" s="461"/>
+      <c r="F124" s="461"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="467" t="s">
+      <c r="B131" s="463" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="467"/>
-      <c r="D131" s="467"/>
-      <c r="E131" s="467"/>
-      <c r="F131" s="467"/>
+      <c r="C131" s="463"/>
+      <c r="D131" s="463"/>
+      <c r="E131" s="463"/>
+      <c r="F131" s="463"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="462" t="s">
+      <c r="B132" s="460" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="462"/>
-      <c r="D132" s="462"/>
-      <c r="E132" s="462"/>
-      <c r="F132" s="462"/>
+      <c r="C132" s="460"/>
+      <c r="D132" s="460"/>
+      <c r="E132" s="460"/>
+      <c r="F132" s="460"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="461" t="s">
+      <c r="B149" s="467" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="462"/>
-      <c r="D149" s="462"/>
-      <c r="E149" s="462"/>
-      <c r="F149" s="462"/>
+      <c r="C149" s="460"/>
+      <c r="D149" s="460"/>
+      <c r="E149" s="460"/>
+      <c r="F149" s="460"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="463" t="s">
+      <c r="B158" s="461" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="463"/>
-      <c r="D158" s="463"/>
-      <c r="E158" s="463"/>
-      <c r="F158" s="463"/>
+      <c r="C158" s="461"/>
+      <c r="D158" s="461"/>
+      <c r="E158" s="461"/>
+      <c r="F158" s="461"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="460" t="s">
+      <c r="B161" s="466" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="460"/>
-      <c r="D161" s="460"/>
-      <c r="E161" s="460"/>
-      <c r="F161" s="460"/>
+      <c r="C161" s="466"/>
+      <c r="D161" s="466"/>
+      <c r="E161" s="466"/>
+      <c r="F161" s="466"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="460" t="s">
+      <c r="B162" s="466" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="460"/>
-      <c r="D162" s="460"/>
-      <c r="E162" s="460"/>
-      <c r="F162" s="460"/>
+      <c r="C162" s="466"/>
+      <c r="D162" s="466"/>
+      <c r="E162" s="466"/>
+      <c r="F162" s="466"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,6 +6793,18 @@
     </row>
   </sheetData>
   <mergeCells count="28">
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6809,18 +6821,6 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -20355,13 +20355,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="474" t="s">
+      <c r="B12" s="471" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="474"/>
-      <c r="D12" s="474"/>
-      <c r="E12" s="474"/>
-      <c r="F12" s="474"/>
+      <c r="C12" s="471"/>
+      <c r="D12" s="471"/>
+      <c r="E12" s="471"/>
+      <c r="F12" s="471"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20546,22 +20546,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="474" t="s">
+      <c r="B29" s="471" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="474"/>
-      <c r="D29" s="474"/>
-      <c r="E29" s="474"/>
-      <c r="F29" s="474"/>
+      <c r="C29" s="471"/>
+      <c r="D29" s="471"/>
+      <c r="E29" s="471"/>
+      <c r="F29" s="471"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="477" t="s">
+      <c r="B30" s="472" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="477"/>
-      <c r="D30" s="477"/>
-      <c r="E30" s="477"/>
-      <c r="F30" s="477"/>
+      <c r="C30" s="472"/>
+      <c r="D30" s="472"/>
+      <c r="E30" s="472"/>
+      <c r="F30" s="472"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20751,10 +20751,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="476"/>
-      <c r="D54" s="476"/>
-      <c r="E54" s="476"/>
-      <c r="F54" s="476"/>
+      <c r="C54" s="473"/>
+      <c r="D54" s="473"/>
+      <c r="E54" s="473"/>
+      <c r="F54" s="473"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20770,22 +20770,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="474" t="s">
+      <c r="B57" s="471" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="474"/>
-      <c r="D57" s="474"/>
-      <c r="E57" s="474"/>
-      <c r="F57" s="474"/>
+      <c r="C57" s="471"/>
+      <c r="D57" s="471"/>
+      <c r="E57" s="471"/>
+      <c r="F57" s="471"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="474" t="s">
+      <c r="B58" s="471" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="474"/>
-      <c r="D58" s="474"/>
-      <c r="E58" s="474"/>
-      <c r="F58" s="474"/>
+      <c r="C58" s="471"/>
+      <c r="D58" s="471"/>
+      <c r="E58" s="471"/>
+      <c r="F58" s="471"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20920,22 +20920,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="474" t="s">
+      <c r="B73" s="471" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="474"/>
-      <c r="D73" s="474"/>
-      <c r="E73" s="474"/>
-      <c r="F73" s="474"/>
+      <c r="C73" s="471"/>
+      <c r="D73" s="471"/>
+      <c r="E73" s="471"/>
+      <c r="F73" s="471"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="477" t="s">
+      <c r="B74" s="472" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="477"/>
-      <c r="D74" s="477"/>
-      <c r="E74" s="477"/>
-      <c r="F74" s="477"/>
+      <c r="C74" s="472"/>
+      <c r="D74" s="472"/>
+      <c r="E74" s="472"/>
+      <c r="F74" s="472"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20943,13 +20943,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="474" t="s">
+      <c r="B77" s="471" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="474"/>
-      <c r="D77" s="474"/>
-      <c r="E77" s="474"/>
-      <c r="F77" s="474"/>
+      <c r="C77" s="471"/>
+      <c r="D77" s="471"/>
+      <c r="E77" s="471"/>
+      <c r="F77" s="471"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21098,33 +21098,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="474" t="s">
+      <c r="B96" s="471" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="474"/>
-      <c r="D96" s="474"/>
-      <c r="E96" s="474"/>
-      <c r="F96" s="474"/>
+      <c r="C96" s="471"/>
+      <c r="D96" s="471"/>
+      <c r="E96" s="471"/>
+      <c r="F96" s="471"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="477" t="s">
+      <c r="B97" s="472" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="477"/>
-      <c r="D97" s="477"/>
-      <c r="E97" s="477"/>
-      <c r="F97" s="477"/>
+      <c r="C97" s="472"/>
+      <c r="D97" s="472"/>
+      <c r="E97" s="472"/>
+      <c r="F97" s="472"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="477" t="s">
+      <c r="B98" s="472" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="477"/>
-      <c r="D98" s="477"/>
-      <c r="E98" s="477"/>
-      <c r="F98" s="477"/>
+      <c r="C98" s="472"/>
+      <c r="D98" s="472"/>
+      <c r="E98" s="472"/>
+      <c r="F98" s="472"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21187,23 +21187,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="474" t="s">
+      <c r="B107" s="471" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="474"/>
-      <c r="D107" s="474"/>
-      <c r="E107" s="474"/>
-      <c r="F107" s="474"/>
+      <c r="C107" s="471"/>
+      <c r="D107" s="471"/>
+      <c r="E107" s="471"/>
+      <c r="F107" s="471"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="474" t="s">
+      <c r="B108" s="471" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="474"/>
-      <c r="D108" s="474"/>
-      <c r="E108" s="474"/>
-      <c r="F108" s="474"/>
+      <c r="C108" s="471"/>
+      <c r="D108" s="471"/>
+      <c r="E108" s="471"/>
+      <c r="F108" s="471"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21247,13 +21247,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="474" t="s">
+      <c r="B114" s="471" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="474"/>
-      <c r="D114" s="474"/>
-      <c r="E114" s="474"/>
-      <c r="F114" s="474"/>
+      <c r="C114" s="471"/>
+      <c r="D114" s="471"/>
+      <c r="E114" s="471"/>
+      <c r="F114" s="471"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21417,13 +21417,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="472" t="s">
+      <c r="B127" s="475" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="472"/>
-      <c r="D127" s="472"/>
-      <c r="E127" s="472"/>
-      <c r="F127" s="472"/>
+      <c r="C127" s="475"/>
+      <c r="D127" s="475"/>
+      <c r="E127" s="475"/>
+      <c r="F127" s="475"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21436,22 +21436,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="473" t="s">
+      <c r="B131" s="476" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="473"/>
-      <c r="D131" s="473"/>
-      <c r="E131" s="473"/>
-      <c r="F131" s="473"/>
+      <c r="C131" s="476"/>
+      <c r="D131" s="476"/>
+      <c r="E131" s="476"/>
+      <c r="F131" s="476"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="474" t="s">
+      <c r="B132" s="471" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="474"/>
-      <c r="D132" s="474"/>
-      <c r="E132" s="474"/>
-      <c r="F132" s="474"/>
+      <c r="C132" s="471"/>
+      <c r="D132" s="471"/>
+      <c r="E132" s="471"/>
+      <c r="F132" s="471"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21620,13 +21620,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="475" t="s">
+      <c r="B149" s="477" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="474"/>
-      <c r="D149" s="474"/>
-      <c r="E149" s="474"/>
-      <c r="F149" s="474"/>
+      <c r="C149" s="471"/>
+      <c r="D149" s="471"/>
+      <c r="E149" s="471"/>
+      <c r="F149" s="471"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21634,13 +21634,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="476" t="s">
+      <c r="B152" s="473" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="476"/>
-      <c r="D152" s="476"/>
-      <c r="E152" s="476"/>
-      <c r="F152" s="476"/>
+      <c r="C152" s="473"/>
+      <c r="D152" s="473"/>
+      <c r="E152" s="473"/>
+      <c r="F152" s="473"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21677,22 +21677,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="471" t="s">
+      <c r="B161" s="474" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="471"/>
-      <c r="D161" s="471"/>
-      <c r="E161" s="471"/>
-      <c r="F161" s="471"/>
+      <c r="C161" s="474"/>
+      <c r="D161" s="474"/>
+      <c r="E161" s="474"/>
+      <c r="F161" s="474"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="471" t="s">
+      <c r="B162" s="474" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="471"/>
-      <c r="D162" s="471"/>
-      <c r="E162" s="471"/>
-      <c r="F162" s="471"/>
+      <c r="C162" s="474"/>
+      <c r="D162" s="474"/>
+      <c r="E162" s="474"/>
+      <c r="F162" s="474"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21716,12 +21716,15 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21736,15 +21739,12 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">

--- a/financial_models/opportunities/3998.HK_Valuation.xlsx
+++ b/financial_models/opportunities/3998.HK_Valuation.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\jerry\PycharmProjects\Invest_Proc\financial_models\opportunities\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{3E30E3FF-0CF7-4CB1-9DA6-B40A3843E6C1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C72C3AF-23F5-4382-9AA8-845031724E08}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-98" yWindow="-98" windowWidth="17115" windowHeight="10755" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -4989,30 +4989,30 @@
       <alignment wrapText="1"/>
     </xf>
     <xf numFmtId="10" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="24" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -5022,25 +5022,25 @@
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left"/>
     </xf>
-    <xf numFmtId="0" fontId="54" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="61" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="62" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="65" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="left" wrapText="1"/>
     </xf>
   </cellXfs>
@@ -5410,7 +5410,7 @@
         <v>349</v>
       </c>
       <c r="C8" s="47">
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="E8" s="32"/>
     </row>
@@ -5428,14 +5428,14 @@
       </c>
       <c r="C10" s="33">
         <f>Thesis!C8*Common_Shares/1000000</f>
-        <v>50476.918487039999</v>
+        <v>50710.607924479998</v>
       </c>
       <c r="D10" s="1" t="s">
         <v>527</v>
       </c>
       <c r="E10" s="303">
         <f>Scenarios!F34</f>
-        <v>0.13888640390130119</v>
+        <v>0.13704089439598224</v>
       </c>
     </row>
     <row r="11" spans="1:9">
@@ -5443,13 +5443,13 @@
       <c r="E11" s="5"/>
     </row>
     <row r="12" spans="1:9" ht="24.5" customHeight="1">
-      <c r="B12" s="460" t="s">
+      <c r="B12" s="462" t="s">
         <v>354</v>
       </c>
-      <c r="C12" s="460"/>
-      <c r="D12" s="460"/>
-      <c r="E12" s="460"/>
-      <c r="F12" s="460"/>
+      <c r="C12" s="462"/>
+      <c r="D12" s="462"/>
+      <c r="E12" s="462"/>
+      <c r="F12" s="462"/>
     </row>
     <row r="14" spans="1:9">
       <c r="B14" s="42" t="str">
@@ -5627,22 +5627,22 @@
       <c r="F27" s="34"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="460" t="s">
+      <c r="B29" s="462" t="s">
         <v>355</v>
       </c>
-      <c r="C29" s="460"/>
-      <c r="D29" s="460"/>
-      <c r="E29" s="460"/>
-      <c r="F29" s="460"/>
+      <c r="C29" s="462"/>
+      <c r="D29" s="462"/>
+      <c r="E29" s="462"/>
+      <c r="F29" s="462"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="462" t="s">
+      <c r="B30" s="466" t="s">
         <v>265</v>
       </c>
-      <c r="C30" s="462"/>
-      <c r="D30" s="462"/>
-      <c r="E30" s="462"/>
-      <c r="F30" s="462"/>
+      <c r="C30" s="466"/>
+      <c r="D30" s="466"/>
+      <c r="E30" s="466"/>
+      <c r="F30" s="466"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="192" t="s">
@@ -5654,13 +5654,13 @@
       </c>
     </row>
     <row r="33" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B33" s="461" t="s">
+      <c r="B33" s="463" t="s">
         <v>195</v>
       </c>
-      <c r="C33" s="461"/>
-      <c r="D33" s="461"/>
-      <c r="E33" s="461"/>
-      <c r="F33" s="461"/>
+      <c r="C33" s="463"/>
+      <c r="D33" s="463"/>
+      <c r="E33" s="463"/>
+      <c r="F33" s="463"/>
     </row>
     <row r="34" spans="2:6">
       <c r="B34" s="44" t="s">
@@ -5680,13 +5680,13 @@
       <c r="C35" s="73"/>
     </row>
     <row r="36" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B36" s="461" t="s">
+      <c r="B36" s="463" t="s">
         <v>197</v>
       </c>
-      <c r="C36" s="461"/>
-      <c r="D36" s="461"/>
-      <c r="E36" s="461"/>
-      <c r="F36" s="461"/>
+      <c r="C36" s="463"/>
+      <c r="D36" s="463"/>
+      <c r="E36" s="463"/>
+      <c r="F36" s="463"/>
     </row>
     <row r="37" spans="2:6">
       <c r="B37" s="44" t="s">
@@ -5715,13 +5715,13 @@
       </c>
     </row>
     <row r="40" spans="2:6">
-      <c r="B40" s="461" t="s">
+      <c r="B40" s="463" t="s">
         <v>200</v>
       </c>
-      <c r="C40" s="461"/>
-      <c r="D40" s="461"/>
-      <c r="E40" s="461"/>
-      <c r="F40" s="461"/>
+      <c r="C40" s="463"/>
+      <c r="D40" s="463"/>
+      <c r="E40" s="463"/>
+      <c r="F40" s="463"/>
     </row>
     <row r="41" spans="2:6">
       <c r="B41" s="44" t="s">
@@ -5737,13 +5737,13 @@
       </c>
     </row>
     <row r="43" spans="2:6">
-      <c r="B43" s="461" t="s">
+      <c r="B43" s="463" t="s">
         <v>204</v>
       </c>
-      <c r="C43" s="461"/>
-      <c r="D43" s="461"/>
-      <c r="E43" s="461"/>
-      <c r="F43" s="461"/>
+      <c r="C43" s="463"/>
+      <c r="D43" s="463"/>
+      <c r="E43" s="463"/>
+      <c r="F43" s="463"/>
     </row>
     <row r="44" spans="2:6">
       <c r="B44" s="44" t="s">
@@ -5807,13 +5807,13 @@
       </c>
     </row>
     <row r="51" spans="2:6">
-      <c r="B51" s="461" t="s">
+      <c r="B51" s="463" t="s">
         <v>205</v>
       </c>
-      <c r="C51" s="461"/>
-      <c r="D51" s="461"/>
-      <c r="E51" s="461"/>
-      <c r="F51" s="461"/>
+      <c r="C51" s="463"/>
+      <c r="D51" s="463"/>
+      <c r="E51" s="463"/>
+      <c r="F51" s="463"/>
     </row>
     <row r="52" spans="2:6">
       <c r="B52" s="44" t="s">
@@ -5829,7 +5829,7 @@
       </c>
     </row>
     <row r="54" spans="2:6">
-      <c r="B54" s="461" t="s">
+      <c r="B54" s="463" t="s">
         <v>264</v>
       </c>
       <c r="C54" s="464"/>
@@ -5851,22 +5851,22 @@
       </c>
     </row>
     <row r="57" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B57" s="460" t="s">
+      <c r="B57" s="462" t="s">
         <v>269</v>
       </c>
-      <c r="C57" s="460"/>
-      <c r="D57" s="460"/>
-      <c r="E57" s="460"/>
-      <c r="F57" s="460"/>
+      <c r="C57" s="462"/>
+      <c r="D57" s="462"/>
+      <c r="E57" s="462"/>
+      <c r="F57" s="462"/>
     </row>
     <row r="58" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B58" s="460" t="s">
+      <c r="B58" s="462" t="s">
         <v>281</v>
       </c>
-      <c r="C58" s="460"/>
-      <c r="D58" s="460"/>
-      <c r="E58" s="460"/>
-      <c r="F58" s="460"/>
+      <c r="C58" s="462"/>
+      <c r="D58" s="462"/>
+      <c r="E58" s="462"/>
+      <c r="F58" s="462"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="44" t="s">
@@ -5900,7 +5900,7 @@
       </c>
       <c r="C62" s="89">
         <f>Normalized_FCF!C124</f>
-        <v>6.7537394348620633E-2</v>
+        <v>6.7226162116599347E-2</v>
       </c>
       <c r="F62" s="257"/>
     </row>
@@ -5910,7 +5910,7 @@
       </c>
       <c r="C63" s="89">
         <f>Normalized_FCF!C92</f>
-        <v>6.0185185185185182E-2</v>
+        <v>5.9907834101382493E-2</v>
       </c>
       <c r="E63" s="44" t="s">
         <v>321</v>
@@ -6001,13 +6001,13 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="191"/>
-      <c r="B73" s="460" t="s">
+      <c r="B73" s="462" t="s">
         <v>477</v>
       </c>
-      <c r="C73" s="460"/>
-      <c r="D73" s="460"/>
-      <c r="E73" s="460"/>
-      <c r="F73" s="460"/>
+      <c r="C73" s="462"/>
+      <c r="D73" s="462"/>
+      <c r="E73" s="462"/>
+      <c r="F73" s="462"/>
     </row>
     <row r="74" spans="1:6">
       <c r="A74" s="191"/>
@@ -6026,13 +6026,13 @@
     </row>
     <row r="77" spans="1:6">
       <c r="A77" s="191"/>
-      <c r="B77" s="460" t="s">
+      <c r="B77" s="462" t="s">
         <v>270</v>
       </c>
-      <c r="C77" s="460"/>
-      <c r="D77" s="460"/>
-      <c r="E77" s="460"/>
-      <c r="F77" s="460"/>
+      <c r="C77" s="462"/>
+      <c r="D77" s="462"/>
+      <c r="E77" s="462"/>
+      <c r="F77" s="462"/>
     </row>
     <row r="78" spans="1:6">
       <c r="A78" s="191"/>
@@ -6201,31 +6201,31 @@
       <c r="A95" s="191"/>
     </row>
     <row r="96" spans="1:6" ht="11.75" customHeight="1">
-      <c r="B96" s="460" t="s">
+      <c r="B96" s="462" t="s">
         <v>484</v>
       </c>
-      <c r="C96" s="460"/>
-      <c r="D96" s="460"/>
-      <c r="E96" s="460"/>
-      <c r="F96" s="460"/>
+      <c r="C96" s="462"/>
+      <c r="D96" s="462"/>
+      <c r="E96" s="462"/>
+      <c r="F96" s="462"/>
     </row>
     <row r="97" spans="2:6">
-      <c r="B97" s="462" t="s">
+      <c r="B97" s="466" t="s">
         <v>483</v>
       </c>
-      <c r="C97" s="462"/>
-      <c r="D97" s="462"/>
-      <c r="E97" s="462"/>
-      <c r="F97" s="462"/>
+      <c r="C97" s="466"/>
+      <c r="D97" s="466"/>
+      <c r="E97" s="466"/>
+      <c r="F97" s="466"/>
     </row>
     <row r="98" spans="2:6">
-      <c r="B98" s="462" t="s">
+      <c r="B98" s="466" t="s">
         <v>482</v>
       </c>
-      <c r="C98" s="462"/>
-      <c r="D98" s="462"/>
-      <c r="E98" s="462"/>
-      <c r="F98" s="462"/>
+      <c r="C98" s="466"/>
+      <c r="D98" s="466"/>
+      <c r="E98" s="466"/>
+      <c r="F98" s="466"/>
     </row>
     <row r="100" spans="2:6">
       <c r="B100" s="192" t="s">
@@ -6275,22 +6275,22 @@
       <c r="C106" s="116"/>
     </row>
     <row r="107" spans="2:6">
-      <c r="B107" s="460" t="s">
+      <c r="B107" s="462" t="s">
         <v>282</v>
       </c>
-      <c r="C107" s="460"/>
-      <c r="D107" s="460"/>
-      <c r="E107" s="460"/>
-      <c r="F107" s="460"/>
+      <c r="C107" s="462"/>
+      <c r="D107" s="462"/>
+      <c r="E107" s="462"/>
+      <c r="F107" s="462"/>
     </row>
     <row r="108" spans="2:6">
-      <c r="B108" s="460" t="s">
+      <c r="B108" s="462" t="s">
         <v>283</v>
       </c>
-      <c r="C108" s="460"/>
-      <c r="D108" s="460"/>
-      <c r="E108" s="460"/>
-      <c r="F108" s="460"/>
+      <c r="C108" s="462"/>
+      <c r="D108" s="462"/>
+      <c r="E108" s="462"/>
+      <c r="F108" s="462"/>
     </row>
     <row r="110" spans="2:6">
       <c r="B110" s="192" t="s">
@@ -6324,13 +6324,13 @@
       </c>
     </row>
     <row r="114" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B114" s="460" t="s">
+      <c r="B114" s="462" t="s">
         <v>490</v>
       </c>
-      <c r="C114" s="460"/>
-      <c r="D114" s="460"/>
-      <c r="E114" s="460"/>
-      <c r="F114" s="460"/>
+      <c r="C114" s="462"/>
+      <c r="D114" s="462"/>
+      <c r="E114" s="462"/>
+      <c r="F114" s="462"/>
     </row>
     <row r="116" spans="2:6">
       <c r="B116" s="192" t="s">
@@ -6465,13 +6465,13 @@
       </c>
     </row>
     <row r="124" spans="2:6">
-      <c r="B124" s="461" t="s">
+      <c r="B124" s="463" t="s">
         <v>356</v>
       </c>
-      <c r="C124" s="461"/>
-      <c r="D124" s="461"/>
-      <c r="E124" s="461"/>
-      <c r="F124" s="461"/>
+      <c r="C124" s="463"/>
+      <c r="D124" s="463"/>
+      <c r="E124" s="463"/>
+      <c r="F124" s="463"/>
     </row>
     <row r="125" spans="2:6">
       <c r="B125" s="193" t="s">
@@ -6506,22 +6506,22 @@
       <c r="F129" s="34"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="463" t="s">
+      <c r="B131" s="467" t="s">
         <v>284</v>
       </c>
-      <c r="C131" s="463"/>
-      <c r="D131" s="463"/>
-      <c r="E131" s="463"/>
-      <c r="F131" s="463"/>
+      <c r="C131" s="467"/>
+      <c r="D131" s="467"/>
+      <c r="E131" s="467"/>
+      <c r="F131" s="467"/>
     </row>
     <row r="132" spans="1:6">
-      <c r="B132" s="460" t="s">
+      <c r="B132" s="462" t="s">
         <v>358</v>
       </c>
-      <c r="C132" s="460"/>
-      <c r="D132" s="460"/>
-      <c r="E132" s="460"/>
-      <c r="F132" s="460"/>
+      <c r="C132" s="462"/>
+      <c r="D132" s="462"/>
+      <c r="E132" s="462"/>
+      <c r="F132" s="462"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="192" t="s">
@@ -6697,13 +6697,13 @@
       <c r="F147" s="34"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="467" t="s">
+      <c r="B149" s="461" t="s">
         <v>359</v>
       </c>
-      <c r="C149" s="460"/>
-      <c r="D149" s="460"/>
-      <c r="E149" s="460"/>
-      <c r="F149" s="460"/>
+      <c r="C149" s="462"/>
+      <c r="D149" s="462"/>
+      <c r="E149" s="462"/>
+      <c r="F149" s="462"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="192" t="s">
@@ -6740,13 +6740,13 @@
       </c>
     </row>
     <row r="158" spans="1:6" ht="34.25" customHeight="1">
-      <c r="B158" s="461" t="s">
+      <c r="B158" s="463" t="s">
         <v>437</v>
       </c>
-      <c r="C158" s="461"/>
-      <c r="D158" s="461"/>
-      <c r="E158" s="461"/>
-      <c r="F158" s="461"/>
+      <c r="C158" s="463"/>
+      <c r="D158" s="463"/>
+      <c r="E158" s="463"/>
+      <c r="F158" s="463"/>
     </row>
     <row r="160" spans="1:6">
       <c r="B160" s="1" t="s">
@@ -6754,22 +6754,22 @@
       </c>
     </row>
     <row r="161" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B161" s="466" t="s">
+      <c r="B161" s="460" t="s">
         <v>293</v>
       </c>
-      <c r="C161" s="466"/>
-      <c r="D161" s="466"/>
-      <c r="E161" s="466"/>
-      <c r="F161" s="466"/>
+      <c r="C161" s="460"/>
+      <c r="D161" s="460"/>
+      <c r="E161" s="460"/>
+      <c r="F161" s="460"/>
     </row>
     <row r="162" spans="2:6" ht="24.5" customHeight="1">
-      <c r="B162" s="466" t="s">
+      <c r="B162" s="460" t="s">
         <v>294</v>
       </c>
-      <c r="C162" s="466"/>
-      <c r="D162" s="466"/>
-      <c r="E162" s="466"/>
-      <c r="F162" s="466"/>
+      <c r="C162" s="460"/>
+      <c r="D162" s="460"/>
+      <c r="E162" s="460"/>
+      <c r="F162" s="460"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="1" t="s">
@@ -6793,18 +6793,6 @@
     </row>
   </sheetData>
   <mergeCells count="28">
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B152:F152"/>
-    <mergeCell ref="B107:F107"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B57:F57"/>
-    <mergeCell ref="B77:F77"/>
-    <mergeCell ref="B73:F73"/>
-    <mergeCell ref="B97:F97"/>
-    <mergeCell ref="B114:F114"/>
     <mergeCell ref="B132:F132"/>
     <mergeCell ref="B40:F40"/>
     <mergeCell ref="B12:F12"/>
@@ -6821,6 +6809,18 @@
     <mergeCell ref="B96:F96"/>
     <mergeCell ref="B98:F98"/>
     <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B107:F107"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B57:F57"/>
+    <mergeCell ref="B77:F77"/>
+    <mergeCell ref="B73:F73"/>
+    <mergeCell ref="B97:F97"/>
+    <mergeCell ref="B114:F114"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <dataValidations count="4">
@@ -14075,16 +14075,16 @@
       </c>
       <c r="C92" s="22">
         <f>(C88*(1-dividend_tax_rate))/Market_Price</f>
-        <v>6.0185185185185182E-2</v>
+        <v>5.9907834101382493E-2</v>
       </c>
       <c r="E92" s="237"/>
       <c r="G92" s="22">
         <f t="shared" ref="G92:Q92" si="38">IF(G$4="","",(G88*(1-dividend_tax_rate))/Market_Price)</f>
-        <v>6.0185185185185182E-2</v>
+        <v>5.9907834101382493E-2</v>
       </c>
       <c r="H92" s="22">
         <f t="shared" si="38"/>
-        <v>5.7870370370370364E-2</v>
+        <v>5.7603686635944701E-2</v>
       </c>
       <c r="I92" s="22">
         <f t="shared" si="38"/>
@@ -15296,34 +15296,34 @@
       </c>
       <c r="C124" s="74">
         <f>C19*Exchange_Rate*$C$3/(Market_Price*Common_Shares)</f>
-        <v>6.7537394348620633E-2</v>
+        <v>6.7226162116599347E-2</v>
       </c>
       <c r="D124" s="26"/>
       <c r="E124" s="234"/>
       <c r="F124" s="26"/>
       <c r="G124" s="74">
         <f t="shared" ref="G124" si="49">IF(G$4="","",G123/Market_Price)</f>
-        <v>6.0166236321959783E-2</v>
+        <v>5.9888972560107445E-2</v>
       </c>
       <c r="H124" s="74">
         <f t="shared" ref="H124" si="50">IF(H$4="","",H123/Market_Price)</f>
-        <v>5.4467403191759502E-2</v>
+        <v>5.4216401333732962E-2</v>
       </c>
       <c r="I124" s="74">
         <f t="shared" ref="I124" si="51">IF(I$4="","",I123/Market_Price)</f>
-        <v>0.18161590429735464</v>
+        <v>0.18077896464621479</v>
       </c>
       <c r="J124" s="74">
         <f t="shared" ref="J124" si="52">IF(J$4="","",J123/Market_Price)</f>
-        <v>0.18021395154622505</v>
+        <v>0.17938347250684156</v>
       </c>
       <c r="K124" s="74">
         <f t="shared" ref="K124" si="53">IF(K$4="","",K123/Market_Price)</f>
-        <v>0.14498968064306988</v>
+        <v>0.14432152543273316</v>
       </c>
       <c r="L124" s="74">
         <f t="shared" ref="L124" si="54">IF(L$4="","",L123/Market_Price)</f>
-        <v>0.12369197169500259</v>
+        <v>0.12312196260885051</v>
       </c>
       <c r="M124" s="74" t="str">
         <f t="shared" ref="M124" si="55">IF(M$4="","",M123/Market_Price)</f>
@@ -15353,27 +15353,27 @@
       <c r="C125" s="151"/>
       <c r="G125" s="22">
         <f>IF(G$4="","",(Data!C47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>7.038351600072755E-2</v>
+        <v>7.0059168000724203E-2</v>
       </c>
       <c r="H125" s="22">
         <f>IF(H$4="","",(Data!D47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>6.1813123572531437E-2</v>
+        <v>6.152827046851056E-2</v>
       </c>
       <c r="I125" s="22">
         <f>IF(I$4="","",(Data!E47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.2367364413282892E-2</v>
+        <v>4.2172123102622611E-2</v>
       </c>
       <c r="J125" s="22">
         <f>IF(J$4="","",(Data!F47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>4.0856753181743921E-2</v>
+        <v>4.0668473213164455E-2</v>
       </c>
       <c r="K125" s="22">
         <f>IF(K$4="","",(Data!G47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>3.3868271900134569E-2</v>
+        <v>3.3712196914419665E-2</v>
       </c>
       <c r="L125" s="22">
         <f>IF(L$4="","",(Data!H47*$C$3)/(Market_Price*Common_Shares))</f>
-        <v>2.3836320363116434E-2</v>
+        <v>2.3726475568816362E-2</v>
       </c>
       <c r="M125" s="22" t="str">
         <f>IF(M$4="","",(Data!I47*$C$3)/(Market_Price*Common_Shares))</f>
@@ -19815,7 +19815,7 @@
       </c>
       <c r="C34" s="146">
         <f>Market_Price</f>
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
       <c r="D34" t="str">
         <f>Market_currency</f>
@@ -19826,7 +19826,7 @@
       </c>
       <c r="F34" s="330">
         <f>RATE(Holding_Period,$C$33,-C34,$C$36)</f>
-        <v>0.13888640390130119</v>
+        <v>0.13704089439598224</v>
       </c>
     </row>
     <row r="35" spans="2:7">
@@ -20322,7 +20322,7 @@
       </c>
       <c r="C8" s="356">
         <f>Market_Price</f>
-        <v>4.32</v>
+        <v>4.34</v>
       </c>
     </row>
     <row r="9" spans="1:10">
@@ -20340,14 +20340,14 @@
       </c>
       <c r="C10" s="357">
         <f>投资主题!C8*Common_Shares/1000000</f>
-        <v>50476.918487039999</v>
+        <v>50710.607924479998</v>
       </c>
       <c r="D10" s="343" t="s">
         <v>528</v>
       </c>
       <c r="E10" s="360">
         <f>Scenarios!F34</f>
-        <v>0.13888640390130119</v>
+        <v>0.13704089439598224</v>
       </c>
     </row>
     <row r="11" spans="1:10">
@@ -20355,13 +20355,13 @@
       <c r="E11" s="349"/>
     </row>
     <row r="12" spans="1:10" ht="24.5" customHeight="1">
-      <c r="B12" s="471" t="s">
+      <c r="B12" s="474" t="s">
         <v>497</v>
       </c>
-      <c r="C12" s="471"/>
-      <c r="D12" s="471"/>
-      <c r="E12" s="471"/>
-      <c r="F12" s="471"/>
+      <c r="C12" s="474"/>
+      <c r="D12" s="474"/>
+      <c r="E12" s="474"/>
+      <c r="F12" s="474"/>
     </row>
     <row r="14" spans="1:10">
       <c r="B14" s="347" t="s">
@@ -20546,22 +20546,22 @@
       <c r="F27" s="345"/>
     </row>
     <row r="29" spans="1:6">
-      <c r="B29" s="471" t="s">
+      <c r="B29" s="474" t="s">
         <v>498</v>
       </c>
-      <c r="C29" s="471"/>
-      <c r="D29" s="471"/>
-      <c r="E29" s="471"/>
-      <c r="F29" s="471"/>
+      <c r="C29" s="474"/>
+      <c r="D29" s="474"/>
+      <c r="E29" s="474"/>
+      <c r="F29" s="474"/>
     </row>
     <row r="30" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B30" s="472" t="s">
+      <c r="B30" s="477" t="s">
         <v>499</v>
       </c>
-      <c r="C30" s="472"/>
-      <c r="D30" s="472"/>
-      <c r="E30" s="472"/>
-      <c r="F30" s="472"/>
+      <c r="C30" s="477"/>
+      <c r="D30" s="477"/>
+      <c r="E30" s="477"/>
+      <c r="F30" s="477"/>
     </row>
     <row r="32" spans="1:6">
       <c r="B32" s="369" t="s">
@@ -20751,10 +20751,10 @@
       <c r="B54" s="470" t="s">
         <v>506</v>
       </c>
-      <c r="C54" s="473"/>
-      <c r="D54" s="473"/>
-      <c r="E54" s="473"/>
-      <c r="F54" s="473"/>
+      <c r="C54" s="476"/>
+      <c r="D54" s="476"/>
+      <c r="E54" s="476"/>
+      <c r="F54" s="476"/>
     </row>
     <row r="55" spans="2:6">
       <c r="B55" s="372" t="s">
@@ -20770,22 +20770,22 @@
       </c>
     </row>
     <row r="57" spans="2:6">
-      <c r="B57" s="471" t="s">
+      <c r="B57" s="474" t="s">
         <v>507</v>
       </c>
-      <c r="C57" s="471"/>
-      <c r="D57" s="471"/>
-      <c r="E57" s="471"/>
-      <c r="F57" s="471"/>
+      <c r="C57" s="474"/>
+      <c r="D57" s="474"/>
+      <c r="E57" s="474"/>
+      <c r="F57" s="474"/>
     </row>
     <row r="58" spans="2:6">
-      <c r="B58" s="471" t="s">
+      <c r="B58" s="474" t="s">
         <v>508</v>
       </c>
-      <c r="C58" s="471"/>
-      <c r="D58" s="471"/>
-      <c r="E58" s="471"/>
-      <c r="F58" s="471"/>
+      <c r="C58" s="474"/>
+      <c r="D58" s="474"/>
+      <c r="E58" s="474"/>
+      <c r="F58" s="474"/>
     </row>
     <row r="60" spans="2:6">
       <c r="B60" s="372" t="s">
@@ -20819,7 +20819,7 @@
       </c>
       <c r="C62" s="378">
         <f>Normalized_FCF!C124</f>
-        <v>6.7537394348620633E-2</v>
+        <v>6.7226162116599347E-2</v>
       </c>
       <c r="F62" s="379"/>
     </row>
@@ -20829,7 +20829,7 @@
       </c>
       <c r="C63" s="378">
         <f>Normalized_FCF!C92</f>
-        <v>6.0185185185185182E-2</v>
+        <v>5.9907834101382493E-2</v>
       </c>
       <c r="E63" s="372" t="s">
         <v>372</v>
@@ -20920,22 +20920,22 @@
     </row>
     <row r="73" spans="1:6">
       <c r="A73" s="386"/>
-      <c r="B73" s="471" t="s">
+      <c r="B73" s="474" t="s">
         <v>509</v>
       </c>
-      <c r="C73" s="471"/>
-      <c r="D73" s="471"/>
-      <c r="E73" s="471"/>
-      <c r="F73" s="471"/>
+      <c r="C73" s="474"/>
+      <c r="D73" s="474"/>
+      <c r="E73" s="474"/>
+      <c r="F73" s="474"/>
     </row>
     <row r="74" spans="1:6">
-      <c r="B74" s="472" t="s">
+      <c r="B74" s="477" t="s">
         <v>478</v>
       </c>
-      <c r="C74" s="472"/>
-      <c r="D74" s="472"/>
-      <c r="E74" s="472"/>
-      <c r="F74" s="472"/>
+      <c r="C74" s="477"/>
+      <c r="D74" s="477"/>
+      <c r="E74" s="477"/>
+      <c r="F74" s="477"/>
     </row>
     <row r="76" spans="1:6">
       <c r="B76" s="369" t="s">
@@ -20943,13 +20943,13 @@
       </c>
     </row>
     <row r="77" spans="1:6">
-      <c r="B77" s="471" t="s">
+      <c r="B77" s="474" t="s">
         <v>510</v>
       </c>
-      <c r="C77" s="471"/>
-      <c r="D77" s="471"/>
-      <c r="E77" s="471"/>
-      <c r="F77" s="471"/>
+      <c r="C77" s="474"/>
+      <c r="D77" s="474"/>
+      <c r="E77" s="474"/>
+      <c r="F77" s="474"/>
     </row>
     <row r="78" spans="1:6">
       <c r="B78" s="343" t="s">
@@ -21098,33 +21098,33 @@
     </row>
     <row r="96" spans="1:6">
       <c r="A96" s="385"/>
-      <c r="B96" s="471" t="s">
+      <c r="B96" s="474" t="s">
         <v>513</v>
       </c>
-      <c r="C96" s="471"/>
-      <c r="D96" s="471"/>
-      <c r="E96" s="471"/>
-      <c r="F96" s="471"/>
+      <c r="C96" s="474"/>
+      <c r="D96" s="474"/>
+      <c r="E96" s="474"/>
+      <c r="F96" s="474"/>
     </row>
     <row r="97" spans="1:6">
       <c r="A97" s="385"/>
-      <c r="B97" s="472" t="s">
+      <c r="B97" s="477" t="s">
         <v>514</v>
       </c>
-      <c r="C97" s="472"/>
-      <c r="D97" s="472"/>
-      <c r="E97" s="472"/>
-      <c r="F97" s="472"/>
+      <c r="C97" s="477"/>
+      <c r="D97" s="477"/>
+      <c r="E97" s="477"/>
+      <c r="F97" s="477"/>
     </row>
     <row r="98" spans="1:6">
       <c r="A98" s="385"/>
-      <c r="B98" s="472" t="s">
+      <c r="B98" s="477" t="s">
         <v>515</v>
       </c>
-      <c r="C98" s="472"/>
-      <c r="D98" s="472"/>
-      <c r="E98" s="472"/>
-      <c r="F98" s="472"/>
+      <c r="C98" s="477"/>
+      <c r="D98" s="477"/>
+      <c r="E98" s="477"/>
+      <c r="F98" s="477"/>
     </row>
     <row r="99" spans="1:6">
       <c r="A99" s="385"/>
@@ -21187,23 +21187,23 @@
     </row>
     <row r="107" spans="1:6">
       <c r="A107" s="385"/>
-      <c r="B107" s="471" t="s">
+      <c r="B107" s="474" t="s">
         <v>516</v>
       </c>
-      <c r="C107" s="471"/>
-      <c r="D107" s="471"/>
-      <c r="E107" s="471"/>
-      <c r="F107" s="471"/>
+      <c r="C107" s="474"/>
+      <c r="D107" s="474"/>
+      <c r="E107" s="474"/>
+      <c r="F107" s="474"/>
     </row>
     <row r="108" spans="1:6">
       <c r="A108" s="385"/>
-      <c r="B108" s="471" t="s">
+      <c r="B108" s="474" t="s">
         <v>535</v>
       </c>
-      <c r="C108" s="471"/>
-      <c r="D108" s="471"/>
-      <c r="E108" s="471"/>
-      <c r="F108" s="471"/>
+      <c r="C108" s="474"/>
+      <c r="D108" s="474"/>
+      <c r="E108" s="474"/>
+      <c r="F108" s="474"/>
     </row>
     <row r="109" spans="1:6">
       <c r="A109" s="385"/>
@@ -21247,13 +21247,13 @@
     </row>
     <row r="114" spans="1:6">
       <c r="A114" s="385"/>
-      <c r="B114" s="471" t="s">
+      <c r="B114" s="474" t="s">
         <v>517</v>
       </c>
-      <c r="C114" s="471"/>
-      <c r="D114" s="471"/>
-      <c r="E114" s="471"/>
-      <c r="F114" s="471"/>
+      <c r="C114" s="474"/>
+      <c r="D114" s="474"/>
+      <c r="E114" s="474"/>
+      <c r="F114" s="474"/>
     </row>
     <row r="115" spans="1:6">
       <c r="A115" s="385"/>
@@ -21417,13 +21417,13 @@
       </c>
     </row>
     <row r="127" spans="1:6">
-      <c r="B127" s="475" t="s">
+      <c r="B127" s="472" t="s">
         <v>519</v>
       </c>
-      <c r="C127" s="475"/>
-      <c r="D127" s="475"/>
-      <c r="E127" s="475"/>
-      <c r="F127" s="475"/>
+      <c r="C127" s="472"/>
+      <c r="D127" s="472"/>
+      <c r="E127" s="472"/>
+      <c r="F127" s="472"/>
     </row>
     <row r="129" spans="1:6" ht="13.9">
       <c r="A129" s="345" t="s">
@@ -21436,22 +21436,22 @@
       <c r="F129" s="345"/>
     </row>
     <row r="131" spans="1:6">
-      <c r="B131" s="476" t="s">
+      <c r="B131" s="473" t="s">
         <v>520</v>
       </c>
-      <c r="C131" s="476"/>
-      <c r="D131" s="476"/>
-      <c r="E131" s="476"/>
-      <c r="F131" s="476"/>
+      <c r="C131" s="473"/>
+      <c r="D131" s="473"/>
+      <c r="E131" s="473"/>
+      <c r="F131" s="473"/>
     </row>
     <row r="132" spans="1:6" ht="24.5" customHeight="1">
-      <c r="B132" s="471" t="s">
+      <c r="B132" s="474" t="s">
         <v>521</v>
       </c>
-      <c r="C132" s="471"/>
-      <c r="D132" s="471"/>
-      <c r="E132" s="471"/>
-      <c r="F132" s="471"/>
+      <c r="C132" s="474"/>
+      <c r="D132" s="474"/>
+      <c r="E132" s="474"/>
+      <c r="F132" s="474"/>
     </row>
     <row r="134" spans="1:6">
       <c r="B134" s="369" t="s">
@@ -21620,13 +21620,13 @@
       <c r="F147" s="345"/>
     </row>
     <row r="149" spans="1:6">
-      <c r="B149" s="477" t="s">
+      <c r="B149" s="475" t="s">
         <v>522</v>
       </c>
-      <c r="C149" s="471"/>
-      <c r="D149" s="471"/>
-      <c r="E149" s="471"/>
-      <c r="F149" s="471"/>
+      <c r="C149" s="474"/>
+      <c r="D149" s="474"/>
+      <c r="E149" s="474"/>
+      <c r="F149" s="474"/>
     </row>
     <row r="151" spans="1:6">
       <c r="B151" s="369" t="s">
@@ -21634,13 +21634,13 @@
       </c>
     </row>
     <row r="152" spans="1:6">
-      <c r="B152" s="473" t="s">
+      <c r="B152" s="476" t="s">
         <v>523</v>
       </c>
-      <c r="C152" s="473"/>
-      <c r="D152" s="473"/>
-      <c r="E152" s="473"/>
-      <c r="F152" s="473"/>
+      <c r="C152" s="476"/>
+      <c r="D152" s="476"/>
+      <c r="E152" s="476"/>
+      <c r="F152" s="476"/>
     </row>
     <row r="153" spans="1:6">
       <c r="B153" s="412" t="s">
@@ -21677,22 +21677,22 @@
       </c>
     </row>
     <row r="161" spans="2:6">
-      <c r="B161" s="474" t="s">
+      <c r="B161" s="471" t="s">
         <v>387</v>
       </c>
-      <c r="C161" s="474"/>
-      <c r="D161" s="474"/>
-      <c r="E161" s="474"/>
-      <c r="F161" s="474"/>
+      <c r="C161" s="471"/>
+      <c r="D161" s="471"/>
+      <c r="E161" s="471"/>
+      <c r="F161" s="471"/>
     </row>
     <row r="162" spans="2:6">
-      <c r="B162" s="474" t="s">
+      <c r="B162" s="471" t="s">
         <v>388</v>
       </c>
-      <c r="C162" s="474"/>
-      <c r="D162" s="474"/>
-      <c r="E162" s="474"/>
-      <c r="F162" s="474"/>
+      <c r="C162" s="471"/>
+      <c r="D162" s="471"/>
+      <c r="E162" s="471"/>
+      <c r="F162" s="471"/>
     </row>
     <row r="164" spans="2:6">
       <c r="B164" s="343" t="s">
@@ -21716,15 +21716,12 @@
     </row>
   </sheetData>
   <mergeCells count="29">
-    <mergeCell ref="B158:F158"/>
-    <mergeCell ref="B161:F161"/>
-    <mergeCell ref="B162:F162"/>
-    <mergeCell ref="B124:F124"/>
-    <mergeCell ref="B127:F127"/>
-    <mergeCell ref="B131:F131"/>
-    <mergeCell ref="B132:F132"/>
-    <mergeCell ref="B149:F149"/>
-    <mergeCell ref="B152:F152"/>
+    <mergeCell ref="B40:F40"/>
+    <mergeCell ref="B12:F12"/>
+    <mergeCell ref="B29:F29"/>
+    <mergeCell ref="B30:F30"/>
+    <mergeCell ref="B33:F33"/>
+    <mergeCell ref="B36:F36"/>
     <mergeCell ref="B114:F114"/>
     <mergeCell ref="B43:F43"/>
     <mergeCell ref="B51:F51"/>
@@ -21739,12 +21736,15 @@
     <mergeCell ref="B77:F77"/>
     <mergeCell ref="B97:F97"/>
     <mergeCell ref="B98:F98"/>
-    <mergeCell ref="B40:F40"/>
-    <mergeCell ref="B12:F12"/>
-    <mergeCell ref="B29:F29"/>
-    <mergeCell ref="B30:F30"/>
-    <mergeCell ref="B33:F33"/>
-    <mergeCell ref="B36:F36"/>
+    <mergeCell ref="B158:F158"/>
+    <mergeCell ref="B161:F161"/>
+    <mergeCell ref="B162:F162"/>
+    <mergeCell ref="B124:F124"/>
+    <mergeCell ref="B127:F127"/>
+    <mergeCell ref="B131:F131"/>
+    <mergeCell ref="B132:F132"/>
+    <mergeCell ref="B149:F149"/>
+    <mergeCell ref="B152:F152"/>
   </mergeCells>
   <dataValidations count="4">
     <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F4" xr:uid="{42FF33A6-1E0C-4B43-92BC-7EAB9273C898}">
